--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -531,7 +531,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -540,10 +540,10 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>53.85</v>
+        <v>52.63</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -668,13 +668,13 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>53.85</v>
+        <v>52.63</v>
       </c>
       <c r="H2">
         <v>6.4</v>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -82,7 +82,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>FUENTES</t>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
@@ -91,16 +91,25 @@
     <t>MOSCOSO</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>ROSALES</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>ELIZALDE</t>
   </si>
   <si>
-    <t>DAMIAN</t>
+    <t>BERMUDEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
@@ -109,16 +118,25 @@
     <t>LEYVA</t>
   </si>
   <si>
-    <t>CUAQUEHUA</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>VIVIANA JOSELIN</t>
+    <t>YAMILETH</t>
   </si>
   <si>
     <t>MIGUEL ENRIQUE</t>
@@ -127,10 +145,19 @@
     <t>BRISSIA SINAHI</t>
   </si>
   <si>
-    <t>JENNIFER</t>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
   </si>
   <si>
     <t>DORIAN</t>
+  </si>
+  <si>
+    <t>EDUARDO EMER</t>
   </si>
   <si>
     <t>JOSE CARMELO</t>
@@ -531,7 +558,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -540,10 +567,10 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>52.63</v>
+        <v>53.85</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -583,13 +610,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>86.11</v>
+        <v>88.89</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -668,13 +695,13 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -796,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -805,10 +832,10 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>52.63</v>
+        <v>53.85</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -848,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>86.11</v>
+        <v>88.89</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -893,7 +920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,16 +952,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920248</v>
+        <v>23330051920226</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -954,10 +981,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -977,10 +1004,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -994,16 +1021,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920262</v>
+        <v>23330051920260</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1017,16 +1044,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920207</v>
+        <v>23330051920280</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1040,24 +1067,93 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920298</v>
+        <v>22330051920299</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920150</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920298</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="G7">
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -85,22 +85,13 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CALVA</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>MOSCOSO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>BAEZ</t>
@@ -112,22 +103,13 @@
     <t>BERMUDEZ</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>MONTERROSAS</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
@@ -139,22 +121,13 @@
     <t>YAMILETH</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
     <t>MIGUEL ENRIQUE</t>
   </si>
   <si>
-    <t>BRISSIA SINAHI</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>DORIAN</t>
+    <t>ANEL</t>
   </si>
   <si>
     <t>EDUARDO EMER</t>
@@ -698,16 +671,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -741,16 +717,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>86.11</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -764,16 +743,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H5">
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -829,13 +811,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>53.85</v>
+        <v>56.41</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -875,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>88.89</v>
+        <v>86.11</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -910,7 +892,7 @@
         <v>93.33</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,10 +940,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -975,16 +957,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -998,16 +980,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920344</v>
+        <v>23330051920254</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1021,16 +1003,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920260</v>
+        <v>23330051920275</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1044,116 +1026,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920280</v>
+        <v>22330051920150</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920299</v>
+        <v>22330051920298</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920207</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920150</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920298</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,60 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
   </si>
 </sst>
 </file>
@@ -811,16 +757,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>82.05</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -857,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>86.11</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -883,16 +829,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -902,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -932,144 +878,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920226</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920215</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920254</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920275</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920150</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920298</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CLAUDIA RUBI</t>
   </si>
 </sst>
 </file>
@@ -848,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -878,6 +887,29 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920214</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CLAUDIA RUBI</t>
   </si>
 </sst>
 </file>
@@ -512,16 +503,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="G3">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -649,16 +646,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G3">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -786,16 +789,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="G3">
+        <v>72.97</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -857,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -887,29 +896,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920214</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -778,7 +778,7 @@
         <v>82.05</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -830,7 +830,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20231.xlsx
@@ -778,7 +778,7 @@
         <v>82.05</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -830,7 +830,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
